--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -4248,10 +4248,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121123753</v>
+        <v>121112789</v>
       </c>
       <c r="B31" t="n">
-        <v>94690</v>
+        <v>90711</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4260,25 +4260,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>210</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4286,27 +4286,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Stora Körkroka, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>693370</v>
+        <v>693588</v>
       </c>
       <c r="R31" t="n">
-        <v>6551587</v>
+        <v>6551461</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4333,14 +4328,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Murken låga/rotvälta. Troligt återfynd</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4349,29 +4349,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121112789</v>
+        <v>121123753</v>
       </c>
       <c r="B32" t="n">
-        <v>90701</v>
+        <v>94700</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4380,25 +4379,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4406,22 +4405,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Körkroka, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693588</v>
+        <v>693370</v>
       </c>
       <c r="R32" t="n">
-        <v>6551461</v>
+        <v>6551587</v>
       </c>
       <c r="S32" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4448,19 +4452,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:27</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Murken låga/rotvälta. Troligt återfynd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4469,18 +4468,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121125907</v>
+        <v>121125902</v>
       </c>
       <c r="B34" t="n">
-        <v>5169</v>
+        <v>79219</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4601,25 +4601,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693567</v>
+        <v>693633</v>
       </c>
       <c r="R34" t="n">
-        <v>6551451</v>
+        <v>6551455</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121125902</v>
+        <v>121125907</v>
       </c>
       <c r="B35" t="n">
-        <v>79216</v>
+        <v>5169</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4703,25 +4703,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693633</v>
+        <v>693567</v>
       </c>
       <c r="R35" t="n">
-        <v>6551455</v>
+        <v>6551451</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4796,7 +4796,7 @@
         <v>121228868</v>
       </c>
       <c r="B36" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>121125903</v>
       </c>
       <c r="B37" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>121326908</v>
       </c>
       <c r="B38" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -4248,10 +4248,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121112789</v>
+        <v>121123753</v>
       </c>
       <c r="B31" t="n">
-        <v>90711</v>
+        <v>94700</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4260,25 +4260,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4286,22 +4286,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Körkroka, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>693588</v>
+        <v>693370</v>
       </c>
       <c r="R31" t="n">
-        <v>6551461</v>
+        <v>6551587</v>
       </c>
       <c r="S31" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4328,19 +4333,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:27</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Murken låga/rotvälta. Troligt återfynd</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4349,28 +4349,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121123753</v>
+        <v>121112789</v>
       </c>
       <c r="B32" t="n">
-        <v>94700</v>
+        <v>90711</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4379,25 +4380,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>210</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4405,27 +4406,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Stora Körkroka, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693370</v>
+        <v>693588</v>
       </c>
       <c r="R32" t="n">
-        <v>6551587</v>
+        <v>6551461</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4452,14 +4448,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Murken låga/rotvälta. Troligt återfynd</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4468,29 +4469,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121125906</v>
+        <v>121125902</v>
       </c>
       <c r="B33" t="n">
-        <v>8432</v>
+        <v>79219</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4499,25 +4499,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693486</v>
+        <v>693633</v>
       </c>
       <c r="R33" t="n">
-        <v>6551583</v>
+        <v>6551455</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121125902</v>
+        <v>121125906</v>
       </c>
       <c r="B34" t="n">
-        <v>79219</v>
+        <v>8432</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4601,25 +4601,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693633</v>
+        <v>693486</v>
       </c>
       <c r="R34" t="n">
-        <v>6551455</v>
+        <v>6551583</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -4251,7 +4251,7 @@
         <v>121123753</v>
       </c>
       <c r="B31" t="n">
-        <v>94700</v>
+        <v>94712</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>121112789</v>
       </c>
       <c r="B32" t="n">
-        <v>90711</v>
+        <v>90723</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4487,10 +4487,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121125902</v>
+        <v>121125907</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>5169</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4499,25 +4499,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693633</v>
+        <v>693567</v>
       </c>
       <c r="R33" t="n">
-        <v>6551455</v>
+        <v>6551451</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121125907</v>
+        <v>121125902</v>
       </c>
       <c r="B35" t="n">
-        <v>5169</v>
+        <v>79222</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4703,25 +4703,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693567</v>
+        <v>693633</v>
       </c>
       <c r="R35" t="n">
-        <v>6551451</v>
+        <v>6551455</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4911,7 +4911,7 @@
         <v>121125903</v>
       </c>
       <c r="B37" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>121326908</v>
       </c>
       <c r="B38" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -4248,10 +4248,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121123753</v>
+        <v>121112789</v>
       </c>
       <c r="B31" t="n">
-        <v>94712</v>
+        <v>90724</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4260,25 +4260,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>210</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4286,27 +4286,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Stora Körkroka, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>693370</v>
+        <v>693588</v>
       </c>
       <c r="R31" t="n">
-        <v>6551587</v>
+        <v>6551461</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4333,14 +4328,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Murken låga/rotvälta. Troligt återfynd</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4349,29 +4349,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121112789</v>
+        <v>121123753</v>
       </c>
       <c r="B32" t="n">
-        <v>90723</v>
+        <v>94713</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4380,25 +4379,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4406,22 +4405,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Körkroka, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693588</v>
+        <v>693370</v>
       </c>
       <c r="R32" t="n">
-        <v>6551461</v>
+        <v>6551587</v>
       </c>
       <c r="S32" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4448,19 +4452,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:27</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Murken låga/rotvälta. Troligt återfynd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4469,28 +4468,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121125907</v>
+        <v>121125906</v>
       </c>
       <c r="B33" t="n">
-        <v>5169</v>
+        <v>8432</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4503,21 +4503,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693567</v>
+        <v>693486</v>
       </c>
       <c r="R33" t="n">
-        <v>6551451</v>
+        <v>6551583</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121125906</v>
+        <v>121125907</v>
       </c>
       <c r="B34" t="n">
-        <v>8432</v>
+        <v>5169</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693486</v>
+        <v>693567</v>
       </c>
       <c r="R34" t="n">
-        <v>6551583</v>
+        <v>6551451</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4911,7 +4911,7 @@
         <v>121125903</v>
       </c>
       <c r="B37" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>121326908</v>
       </c>
       <c r="B38" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -4248,10 +4248,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121112789</v>
+        <v>121123753</v>
       </c>
       <c r="B31" t="n">
-        <v>90724</v>
+        <v>94716</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4260,25 +4260,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4286,22 +4286,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Körkroka, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>693588</v>
+        <v>693370</v>
       </c>
       <c r="R31" t="n">
-        <v>6551461</v>
+        <v>6551587</v>
       </c>
       <c r="S31" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4328,19 +4333,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:27</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Murken låga/rotvälta. Troligt återfynd</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4349,28 +4349,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121123753</v>
+        <v>121112789</v>
       </c>
       <c r="B32" t="n">
-        <v>94713</v>
+        <v>90727</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4379,25 +4380,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>210</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4405,27 +4406,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Stora Körkroka, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693370</v>
+        <v>693588</v>
       </c>
       <c r="R32" t="n">
-        <v>6551587</v>
+        <v>6551461</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4452,14 +4448,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Murken låga/rotvälta. Troligt återfynd</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4468,29 +4469,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121125906</v>
+        <v>121125907</v>
       </c>
       <c r="B33" t="n">
-        <v>8432</v>
+        <v>5172</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4503,21 +4503,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693486</v>
+        <v>693567</v>
       </c>
       <c r="R33" t="n">
-        <v>6551583</v>
+        <v>6551451</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121125907</v>
+        <v>121125906</v>
       </c>
       <c r="B34" t="n">
-        <v>5169</v>
+        <v>8435</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693567</v>
+        <v>693486</v>
       </c>
       <c r="R34" t="n">
-        <v>6551451</v>
+        <v>6551583</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4694,7 +4694,7 @@
         <v>121125902</v>
       </c>
       <c r="B35" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>121228868</v>
       </c>
       <c r="B36" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>121125903</v>
       </c>
       <c r="B37" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>121326908</v>
       </c>
       <c r="B38" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -4248,10 +4248,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121123753</v>
+        <v>121112789</v>
       </c>
       <c r="B31" t="n">
-        <v>94716</v>
+        <v>90727</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4260,25 +4260,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>210</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4286,27 +4286,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Stora Körkroka, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>693370</v>
+        <v>693588</v>
       </c>
       <c r="R31" t="n">
-        <v>6551587</v>
+        <v>6551461</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4333,14 +4328,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Murken låga/rotvälta. Troligt återfynd</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4349,29 +4349,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121112789</v>
+        <v>121123753</v>
       </c>
       <c r="B32" t="n">
-        <v>90727</v>
+        <v>94716</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4380,25 +4379,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4406,22 +4405,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Körkroka, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693588</v>
+        <v>693370</v>
       </c>
       <c r="R32" t="n">
-        <v>6551461</v>
+        <v>6551587</v>
       </c>
       <c r="S32" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4448,19 +4452,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:27</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Murken låga/rotvälta. Troligt återfynd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4469,28 +4468,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121125907</v>
+        <v>121125902</v>
       </c>
       <c r="B33" t="n">
-        <v>5172</v>
+        <v>79225</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4499,25 +4499,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693567</v>
+        <v>693633</v>
       </c>
       <c r="R33" t="n">
-        <v>6551451</v>
+        <v>6551455</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121125902</v>
+        <v>121125907</v>
       </c>
       <c r="B35" t="n">
-        <v>79225</v>
+        <v>5172</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4703,25 +4703,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693633</v>
+        <v>693567</v>
       </c>
       <c r="R35" t="n">
-        <v>6551455</v>
+        <v>6551451</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -4796,7 +4796,7 @@
         <v>121228868</v>
       </c>
       <c r="B36" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>121125903</v>
       </c>
       <c r="B37" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>121326908</v>
       </c>
       <c r="B38" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -4796,7 +4796,7 @@
         <v>121228868</v>
       </c>
       <c r="B36" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>121125903</v>
       </c>
       <c r="B37" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>121326908</v>
       </c>
       <c r="B38" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -4911,7 +4911,7 @@
         <v>121125903</v>
       </c>
       <c r="B37" t="n">
-        <v>90720</v>
+        <v>90725</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>121326908</v>
       </c>
       <c r="B38" t="n">
-        <v>97059</v>
+        <v>97067</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97612355</v>
+        <v>99519443</v>
       </c>
       <c r="B2" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>693472.552237385</v>
+        <v>693351</v>
       </c>
       <c r="R2" t="n">
-        <v>6551557.540210964</v>
+        <v>6551587</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,65 +765,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99519429</v>
+        <v>121123753</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693530.9306190538</v>
+        <v>693370</v>
       </c>
       <c r="R3" t="n">
-        <v>6551454.362032568</v>
+        <v>6551587</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,27 +854,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Murken låga/rotvälta. Troligt återfynd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,33 +873,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99519424</v>
+        <v>111541120</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693447.8097560777</v>
+        <v>693513</v>
       </c>
       <c r="R4" t="n">
-        <v>6551516.103994695</v>
+        <v>6551518</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,27 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,31 +973,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>silverstubbe av tall</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99505424</v>
+        <v>111541121</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,38 +1010,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693352.0983209984</v>
+        <v>693461</v>
       </c>
       <c r="R5" t="n">
-        <v>6551592.150474994</v>
+        <v>6551521</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,22 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,31 +1080,36 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>silverstubbe av tall</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99505353</v>
+        <v>111541115</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,40 +1117,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693370.3236516167</v>
+        <v>693613</v>
       </c>
       <c r="R6" t="n">
-        <v>6551588.950141247</v>
+        <v>6551435</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,27 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,69 +1187,77 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>låga av gran</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99519445</v>
+        <v>121125903</v>
       </c>
       <c r="B7" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>693460.7380065027</v>
+        <v>693618</v>
       </c>
       <c r="R7" t="n">
-        <v>6551556.427589005</v>
+        <v>6551432</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,27 +1281,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>4 exemplar</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,55 +1295,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99519443</v>
+        <v>121125904</v>
       </c>
       <c r="B8" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,13 +1349,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>693351.3284537568</v>
+        <v>693626</v>
       </c>
       <c r="R8" t="n">
-        <v>6551586.959722023</v>
+        <v>6551421</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,27 +1379,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,65 +1399,63 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111541118</v>
+        <v>121229086</v>
       </c>
       <c r="B9" t="n">
-        <v>94851</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>693461.6376634488</v>
+        <v>693626</v>
       </c>
       <c r="R9" t="n">
-        <v>6551559.049034445</v>
+        <v>6551416</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,22 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,38 +1493,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111541119</v>
+        <v>121229141</v>
       </c>
       <c r="B10" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,46 +1523,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>693467.6220677271</v>
+        <v>693632</v>
       </c>
       <c r="R10" t="n">
-        <v>6551532.561666255</v>
+        <v>6551404</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,27 +1580,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>En gammal tall med kläckhål här och var. Om det är färskt eller gammalt är svårt sia om.</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,78 +1598,70 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>gammeltall</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111541120</v>
+        <v>121112789</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Stora Körkroka, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>693513.2669972532</v>
+        <v>693588</v>
       </c>
       <c r="R11" t="n">
-        <v>6551517.868690074</v>
+        <v>6551461</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,22 +1685,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,41 +1711,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>silverstubbe av tall</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111541128</v>
+        <v>99506087</v>
       </c>
       <c r="B12" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,46 +1738,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693570.8046739453</v>
+        <v>693478</v>
       </c>
       <c r="R12" t="n">
-        <v>6551451.742365629</v>
+        <v>6551421</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1946,22 +1794,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,82 +1818,67 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111541115</v>
+        <v>112175137</v>
       </c>
       <c r="B13" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Stora Körkroka, Stora Körkroka, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693612.9253791923</v>
+        <v>693521</v>
       </c>
       <c r="R13" t="n">
-        <v>6551435.326171798</v>
+        <v>6551438</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2069,22 +1902,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,41 +1928,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>låga av gran</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111541129</v>
+        <v>112175179</v>
       </c>
       <c r="B14" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,46 +1955,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Stora Körkroka, Stora Körkroka, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>693328.6441019299</v>
+        <v>693484</v>
       </c>
       <c r="R14" t="n">
-        <v>6551545.628735202</v>
+        <v>6551529</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2200,22 +2010,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,66 +2034,50 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111541121</v>
+        <v>111541118</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2293,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>693460.9606228607</v>
+        <v>693461</v>
       </c>
       <c r="R15" t="n">
-        <v>6551521.405726598</v>
+        <v>6551559</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,21 +2120,11 @@
           <t>2023-08-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-15</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2353,11 +2137,6 @@
       <c r="AI15" t="inlineStr">
         <is>
           <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>silverstubbe av tall</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2375,59 +2154,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111541122</v>
+        <v>112170161</v>
       </c>
       <c r="B16" t="n">
-        <v>5112</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>693344.0451535647</v>
+        <v>693460</v>
       </c>
       <c r="R16" t="n">
-        <v>6551526.82974836</v>
+        <v>6551545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2454,22 +2219,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2478,88 +2243,63 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>låga av gran</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112170154</v>
+        <v>112170171</v>
       </c>
       <c r="B17" t="n">
-        <v>90896</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5448</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>693475</v>
+        <v>693557</v>
       </c>
       <c r="R17" t="n">
-        <v>6551609</v>
+        <v>6551601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2591,7 +2331,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2601,7 +2341,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2612,6 +2352,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Grov barrträdslåga.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2628,37 +2373,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112170166</v>
+        <v>112170160</v>
       </c>
       <c r="B18" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2668,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>693564</v>
+        <v>693346</v>
       </c>
       <c r="R18" t="n">
-        <v>6551561</v>
+        <v>6551559</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2703,7 +2443,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2713,12 +2453,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Högstubbe från gran med stora hackade hål från födosök.</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2745,37 +2480,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112170155</v>
+        <v>112170168</v>
       </c>
       <c r="B19" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2785,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>693475</v>
+        <v>693568</v>
       </c>
       <c r="R19" t="n">
-        <v>6551610</v>
+        <v>6551574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,7 +2550,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2830,7 +2560,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,9 +2572,24 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Klen tallåga i sumpmark.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Klen tallåga i sumpmark.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2862,15 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112170169</v>
+        <v>99519445</v>
       </c>
       <c r="B20" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2878,42 +2618,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>693585</v>
+        <v>693460</v>
       </c>
       <c r="R20" t="n">
-        <v>6551594</v>
+        <v>6551556</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2937,22 +2672,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>4 exemplar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2963,89 +2693,65 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Björklåga med delar av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Betula # Björklåga med delar av barken kvar.</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112170168</v>
+        <v>99505424</v>
       </c>
       <c r="B21" t="n">
-        <v>93373</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>693567</v>
+        <v>693352</v>
       </c>
       <c r="R21" t="n">
-        <v>6551575</v>
+        <v>6551592</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3069,22 +2775,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3095,51 +2801,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Klen tallåga i sumpmark.</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Klen tallåga i sumpmark.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112170165</v>
+        <v>99506083</v>
       </c>
       <c r="B22" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3147,37 +2828,47 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>693518</v>
+        <v>693478</v>
       </c>
       <c r="R22" t="n">
-        <v>6551573</v>
+        <v>6551421</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3201,27 +2892,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Granlåga med hål från hål från födosök då granen levde.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3236,27 +2922,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112170170</v>
+        <v>99519424</v>
       </c>
       <c r="B23" t="n">
-        <v>56606</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,37 +2945,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>693557</v>
+        <v>693448</v>
       </c>
       <c r="R23" t="n">
-        <v>6551604</v>
+        <v>6551516</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3318,22 +2999,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3348,65 +3024,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112170171</v>
+        <v>99519426</v>
       </c>
       <c r="B24" t="n">
-        <v>94379</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2590</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>693557</v>
+        <v>693444</v>
       </c>
       <c r="R24" t="n">
-        <v>6551601</v>
+        <v>6551500</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3430,22 +3101,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3456,64 +3117,58 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Grov barrträdslåga.</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112170172</v>
+        <v>112170154</v>
       </c>
       <c r="B25" t="n">
-        <v>4727</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>5448</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3522,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>693533</v>
+        <v>693475</v>
       </c>
       <c r="R25" t="n">
-        <v>6551643</v>
+        <v>6551610</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3557,7 +3212,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3567,7 +3222,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3578,26 +3233,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3614,15 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112170162</v>
+        <v>112170155</v>
       </c>
       <c r="B26" t="n">
-        <v>5436</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3630,43 +3260,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101410</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>693467</v>
+        <v>693475</v>
       </c>
       <c r="R26" t="n">
-        <v>6551537</v>
+        <v>6551610</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3698,7 +3319,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3708,7 +3329,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3717,28 +3338,12 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Gammal solbelyst tall med flagnande gulfärgad bark.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal solbelyst tall med flagnande gulfärgad bark.</t>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3756,54 +3361,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112175179</v>
+        <v>112170157</v>
       </c>
       <c r="B27" t="n">
-        <v>93592</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stora Körkroka (Stora Körkroka), Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>693484</v>
+        <v>693304</v>
       </c>
       <c r="R27" t="n">
-        <v>6551530</v>
+        <v>6551503</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3832,7 +3431,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3842,7 +3441,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3853,53 +3452,68 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Tallåga utan splintved på hällmark.</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallåga utan splintved på hällmark.</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112170160</v>
+        <v>112170158</v>
       </c>
       <c r="B28" t="n">
-        <v>93373</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3909,10 +3523,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>693345</v>
+        <v>693297</v>
       </c>
       <c r="R28" t="n">
-        <v>6551560</v>
+        <v>6551510</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3944,7 +3558,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3954,7 +3568,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3965,6 +3579,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Tallstubbe på hällmark.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallstubbe på hällmark.</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3981,53 +3615,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112170161</v>
+        <v>121125902</v>
       </c>
       <c r="B29" t="n">
-        <v>95059</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2569</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>693460</v>
+        <v>693633</v>
       </c>
       <c r="R29" t="n">
-        <v>6551545</v>
+        <v>6551455</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4051,22 +3680,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4081,27 +3700,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112170164</v>
+        <v>99505353</v>
       </c>
       <c r="B30" t="n">
-        <v>4727</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4109,54 +3723,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>693510</v>
+        <v>693370</v>
       </c>
       <c r="R30" t="n">
-        <v>6551542</v>
+        <v>6551589</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4180,27 +3780,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Larv under barkflaga med ett kläckhål.</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4209,99 +3809,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121112789</v>
+        <v>99519429</v>
       </c>
       <c r="B31" t="n">
-        <v>90727</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Körkroka, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>693588</v>
+        <v>693531</v>
       </c>
       <c r="R31" t="n">
-        <v>6551461</v>
+        <v>6551454</v>
       </c>
       <c r="S31" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4325,22 +3892,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4355,27 +3917,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121123753</v>
+        <v>112170165</v>
       </c>
       <c r="B32" t="n">
-        <v>94716</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4383,46 +3940,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693370</v>
+        <v>693519</v>
       </c>
       <c r="R32" t="n">
-        <v>6551587</v>
+        <v>6551573</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4449,17 +3994,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Murken låga/rotvälta. Troligt återfynd</t>
+          <t>Granlåga med hål från hål från födosök då granen levde.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4468,72 +4023,66 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121125902</v>
+        <v>112170166</v>
       </c>
       <c r="B33" t="n">
-        <v>79225</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693633</v>
+        <v>693563</v>
       </c>
       <c r="R33" t="n">
-        <v>6551455</v>
+        <v>6551561</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4557,12 +4106,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Högstubbe från gran med stora hackade hål från födosök.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4577,27 +4141,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121125906</v>
+        <v>121228868</v>
       </c>
       <c r="B34" t="n">
-        <v>8435</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4605,37 +4164,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693486</v>
+        <v>693560</v>
       </c>
       <c r="R34" t="n">
-        <v>6551583</v>
+        <v>6551568</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4659,12 +4226,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>8 stycken hackmärken på högstubb.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4679,27 +4251,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121125907</v>
+        <v>111541128</v>
       </c>
       <c r="B35" t="n">
-        <v>5172</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4725,19 +4292,28 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693567</v>
+        <v>693571</v>
       </c>
       <c r="R35" t="n">
-        <v>6551451</v>
+        <v>6551452</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4761,12 +4337,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4775,79 +4351,86 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121228868</v>
+        <v>111541129</v>
       </c>
       <c r="B36" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Ornö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>693560</v>
+        <v>693329</v>
       </c>
       <c r="R36" t="n">
-        <v>6551568</v>
+        <v>6551546</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4871,17 +4454,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>8 stycken hackmärken på högstubb.</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,71 +4468,74 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121125903</v>
+        <v>121125907</v>
       </c>
       <c r="B37" t="n">
-        <v>90725</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>693618</v>
+        <v>693567</v>
       </c>
       <c r="R37" t="n">
-        <v>6551432</v>
+        <v>6551451</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4995,7 +4576,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5014,54 +4594,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121326908</v>
+        <v>97612355</v>
       </c>
       <c r="B38" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>101410</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693495</v>
+        <v>693473</v>
       </c>
       <c r="R38" t="n">
-        <v>6551538</v>
+        <v>6551558</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5088,12 +4662,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5102,22 +4676,1330 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>111541119</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>693468</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6551532</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>En gammal tall med kläckhål här och var. Om det är färskt eller gammalt är svårt sia om.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>gammeltall</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Karolin Hård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>112170162</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gråberget, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>693467</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6551538</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Gammal solbelyst tall med flagnande gulfärgad bark.</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal solbelyst tall med flagnande gulfärgad bark.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>111541122</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>693344</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6551527</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>låga av gran</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Karolin Hård</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112170164</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gråberget, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>693510</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6551542</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Larv under barkflaga med ett kläckhål.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>112170172</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gråberget, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>693533</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6551644</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>112170170</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gråberget, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>693557</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6551604</v>
+      </c>
+      <c r="S44" t="n">
+        <v>50</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121112440</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora Körkroka, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>693624</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6551396</v>
+      </c>
+      <c r="S45" t="n">
+        <v>9</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121125906</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gråberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>693486</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6551583</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>112170169</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gråberget, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>693585</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6551594</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Björklåga med delar av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Betula # Björklåga med delar av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>99519430</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gråberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>693356</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6551452</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121326908</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gråberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>693495</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6551538</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
           <t>Roja Kirkeby</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX49" t="inlineStr">
         <is>
           <t>Roja Kirkeby</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 67894-2021 artfynd.xlsx
+++ b/artfynd/A 67894-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519443</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121123753</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541120</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541121</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541115</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125903</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125904</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121229086</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121229141</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121112789</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,6 +1888,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99506087</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1941,6 +2001,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112175137</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2049,6 +2114,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112175179</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2151,6 +2221,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541118</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2258,6 +2333,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170161</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2370,6 +2450,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170171</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2477,6 +2562,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170160</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2604,6 +2694,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170168</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2706,6 +2801,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519445</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2814,6 +2914,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99505424</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2931,6 +3036,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99506083</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3033,6 +3143,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519424</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3130,6 +3245,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519426</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3246,6 +3366,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170154</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3358,6 +3483,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170155</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3485,6 +3615,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170157</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3612,6 +3747,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170158</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3709,6 +3849,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125902</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3824,6 +3969,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99505353</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3926,6 +4076,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519429</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4038,6 +4193,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170165</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4150,6 +4310,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170166</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4260,6 +4425,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121228868</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4377,6 +4547,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541128</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4494,6 +4669,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541129</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4591,6 +4771,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125907</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4691,6 +4876,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97612355</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4813,6 +5003,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541119</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4950,6 +5145,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170162</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5067,6 +5267,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541122</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5217,6 +5422,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170164</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5349,6 +5559,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170172</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5456,6 +5671,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170170</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5572,6 +5792,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121112440</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5669,6 +5894,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125906</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5801,6 +6031,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170169</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5898,6 +6133,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519430</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6000,8 +6240,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121326908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>